--- a/data/trans_orig/P78_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P78_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona sustentadora principal trabaja actualmente en 2023</t>
+          <t>Población según si la persona sustentadora principal trabaja actualmente en 2023 (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>206396</t>
+          <t>204705</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>233207</t>
+          <t>233145</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>169282</t>
+          <t>170702</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>195549</t>
+          <t>194233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>387973</t>
+          <t>386352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>425185</t>
+          <t>424974</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,38%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32104</t>
+          <t>33795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52293</t>
+          <t>53609</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78560</t>
+          <t>77140</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61157</t>
+          <t>61368</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98369</t>
+          <t>99990</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>261529</t>
+          <t>261624</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>302447</t>
+          <t>302259</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>243588</t>
+          <t>242990</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>272727</t>
+          <t>271048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>517409</t>
+          <t>519864</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>567595</t>
+          <t>567715</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,75%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>22093</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62823</t>
+          <t>62728</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88944</t>
+          <t>90623</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118083</t>
+          <t>118681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>118428</t>
+          <t>118308</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168614</t>
+          <t>166159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171305</t>
+          <t>172149</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>188450</t>
+          <t>188619</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>165462</t>
+          <t>164101</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>189762</t>
+          <t>188865</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>341916</t>
+          <t>344631</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>373421</t>
+          <t>374700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23387</t>
+          <t>22543</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58048</t>
+          <t>58945</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82348</t>
+          <t>83709</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69081</t>
+          <t>67802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>100586</t>
+          <t>97871</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>170041</t>
+          <t>171251</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189404</t>
+          <t>189690</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>283178</t>
+          <t>287461</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>346550</t>
+          <t>347274</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>472170</t>
+          <t>470585</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>530841</t>
+          <t>524588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7088</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26451</t>
+          <t>25241</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43563</t>
+          <t>42839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>106935</t>
+          <t>102652</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55764</t>
+          <t>62017</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>114435</t>
+          <t>116020</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>123895</t>
+          <t>123947</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129896</t>
+          <t>129887</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>119213</t>
+          <t>119972</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132060</t>
+          <t>132469</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>246206</t>
+          <t>245725</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>261226</t>
+          <t>261063</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,97%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7588</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26614</t>
+          <t>26205</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39461</t>
+          <t>38702</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>29094</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43951</t>
+          <t>44432</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>142860</t>
+          <t>142788</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>159764</t>
+          <t>159989</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>131729</t>
+          <t>131322</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>149615</t>
+          <t>149656</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>281736</t>
+          <t>282156</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>305486</t>
+          <t>306321</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,22%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25132</t>
+          <t>25204</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37651</t>
+          <t>37610</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55537</t>
+          <t>55944</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49772</t>
+          <t>48937</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73522</t>
+          <t>73102</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>387080</t>
+          <t>385731</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>415676</t>
+          <t>415966</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>203281</t>
+          <t>172105</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>589854</t>
+          <t>589216</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>461969</t>
+          <t>467408</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1006620</t>
+          <t>1009013</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,17%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9077</t>
+          <t>8787</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37673</t>
+          <t>39022</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>104419</t>
+          <t>105057</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>490992</t>
+          <t>522168</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>112406</t>
+          <t>110013</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>657057</t>
+          <t>651618</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,23%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>662574</t>
+          <t>664231</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>687948</t>
+          <t>689012</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>417713</t>
+          <t>418636</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>451736</t>
+          <t>451928</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1064805</t>
+          <t>1066395</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1184903</t>
+          <t>1188313</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29052</t>
+          <t>27395</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>132363</t>
+          <t>132171</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>166386</t>
+          <t>165463</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>90822</t>
+          <t>87412</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>210920</t>
+          <t>209330</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2201831</t>
+          <t>2200055</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2279414</t>
+          <t>2279383</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1435238</t>
+          <t>1615442</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2215378</t>
+          <t>2223083</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3739116</t>
+          <t>3712386</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4491567</t>
+          <t>4486477</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,59%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>90475</t>
+          <t>90506</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>168058</t>
+          <t>169834</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>656370</t>
+          <t>648665</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1436510</t>
+          <t>1256306</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>750070</t>
+          <t>755160</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1502521</t>
+          <t>1529251</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P78_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P78_2023-Provincia-trans_orig.xlsx
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>225942</t>
+          <t>230134</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>204705</t>
+          <t>218822</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>233145</t>
+          <t>234999</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>183978</t>
+          <t>206203</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>170702</t>
+          <t>192889</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>194233</t>
+          <t>216329</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>409920</t>
+          <t>436336</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>386352</t>
+          <t>421301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>424974</t>
+          <t>448878</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>88,26%</t>
         </is>
       </c>
     </row>
@@ -838,22 +838,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12558</t>
+          <t>10266</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33795</t>
+          <t>21578</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>63864</t>
+          <t>61978</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53609</t>
+          <t>51852</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77140</t>
+          <t>75292</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>76422</t>
+          <t>72245</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61368</t>
+          <t>59703</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99990</t>
+          <t>87280</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>238500</t>
+          <t>240400</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>238500</t>
+          <t>240400</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>238500</t>
+          <t>240400</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>247842</t>
+          <t>268181</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>247842</t>
+          <t>268181</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>247842</t>
+          <t>268181</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>486342</t>
+          <t>508581</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>486342</t>
+          <t>508581</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>486342</t>
+          <t>508581</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>286595</t>
+          <t>291882</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>261624</t>
+          <t>270953</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>302259</t>
+          <t>307459</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>257576</t>
+          <t>277239</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>242990</t>
+          <t>262284</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>271048</t>
+          <t>292308</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>544171</t>
+          <t>569121</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>519864</t>
+          <t>545844</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>567715</t>
+          <t>589859</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>83,11%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>37757</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22093</t>
+          <t>18610</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62728</t>
+          <t>55116</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>104095</t>
+          <t>106403</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90623</t>
+          <t>91334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118681</t>
+          <t>121358</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>141852</t>
+          <t>140590</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>118308</t>
+          <t>119852</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166159</t>
+          <t>163867</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>324352</t>
+          <t>326069</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>324352</t>
+          <t>326069</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>324352</t>
+          <t>326069</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>361671</t>
+          <t>383642</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>361671</t>
+          <t>383642</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>361671</t>
+          <t>383642</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>686023</t>
+          <t>709711</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>686023</t>
+          <t>709711</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>686023</t>
+          <t>709711</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>182447</t>
+          <t>182538</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>172149</t>
+          <t>172788</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>188619</t>
+          <t>188964</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>177378</t>
+          <t>181953</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>164101</t>
+          <t>170078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>188865</t>
+          <t>192266</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>359826</t>
+          <t>364491</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>344631</t>
+          <t>348836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>374700</t>
+          <t>377300</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,81%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12245</t>
+          <t>11262</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22543</t>
+          <t>21012</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70432</t>
+          <t>69119</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58945</t>
+          <t>58806</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83709</t>
+          <t>80994</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>82676</t>
+          <t>80381</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67802</t>
+          <t>67572</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97871</t>
+          <t>96036</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>194692</t>
+          <t>193800</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>194692</t>
+          <t>193800</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>194692</t>
+          <t>193800</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>247810</t>
+          <t>251072</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>247810</t>
+          <t>251072</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>247810</t>
+          <t>251072</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>442502</t>
+          <t>444872</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>442502</t>
+          <t>444872</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>442502</t>
+          <t>444872</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>182707</t>
+          <t>227156</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171251</t>
+          <t>214033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189690</t>
+          <t>235955</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>312750</t>
+          <t>243904</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>287461</t>
+          <t>227856</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>347274</t>
+          <t>255162</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>495456</t>
+          <t>471060</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>470585</t>
+          <t>448841</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>524588</t>
+          <t>487396</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>85,28%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13785</t>
+          <t>17854</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25241</t>
+          <t>30977</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>77363</t>
+          <t>82627</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42839</t>
+          <t>71369</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102652</t>
+          <t>98675</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>91149</t>
+          <t>100481</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62017</t>
+          <t>84145</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116020</t>
+          <t>122700</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>196492</t>
+          <t>245010</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>196492</t>
+          <t>245010</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>196492</t>
+          <t>245010</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>390113</t>
+          <t>326531</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>390113</t>
+          <t>326531</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>390113</t>
+          <t>326531</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>586605</t>
+          <t>571541</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>586605</t>
+          <t>571541</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>586605</t>
+          <t>571541</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>127678</t>
+          <t>149781</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>123947</t>
+          <t>145738</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129887</t>
+          <t>151985</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>126534</t>
+          <t>141062</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>119972</t>
+          <t>134054</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132469</t>
+          <t>147841</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>254212</t>
+          <t>290843</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>245725</t>
+          <t>282485</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>261063</t>
+          <t>298238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7536</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>32140</t>
+          <t>33393</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26205</t>
+          <t>26614</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38702</t>
+          <t>40401</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>35945</t>
+          <t>37351</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29094</t>
+          <t>29956</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44432</t>
+          <t>45709</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>131483</t>
+          <t>153739</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>131483</t>
+          <t>153739</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>131483</t>
+          <t>153739</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>158674</t>
+          <t>174455</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>158674</t>
+          <t>174455</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>158674</t>
+          <t>174455</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>290157</t>
+          <t>328194</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>290157</t>
+          <t>328194</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>290157</t>
+          <t>328194</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>153204</t>
+          <t>151757</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>142788</t>
+          <t>142631</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>159989</t>
+          <t>157750</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>141372</t>
+          <t>143412</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>131322</t>
+          <t>134127</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>149656</t>
+          <t>152855</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>294576</t>
+          <t>295168</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>282156</t>
+          <t>282805</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>306321</t>
+          <t>305629</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,61%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14788</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8003</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25204</t>
+          <t>23312</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>45894</t>
+          <t>47635</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37610</t>
+          <t>38192</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55944</t>
+          <t>56920</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>60682</t>
+          <t>61821</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48937</t>
+          <t>51360</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73102</t>
+          <t>74184</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>167992</t>
+          <t>165943</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>167992</t>
+          <t>165943</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>167992</t>
+          <t>165943</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>187266</t>
+          <t>191047</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>187266</t>
+          <t>191047</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>187266</t>
+          <t>191047</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>355258</t>
+          <t>356989</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>355258</t>
+          <t>356989</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>355258</t>
+          <t>356989</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>405970</t>
+          <t>466486</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>385731</t>
+          <t>449996</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>415966</t>
+          <t>476376</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>409810</t>
+          <t>488476</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>172105</t>
+          <t>470217</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>589216</t>
+          <t>504355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>815781</t>
+          <t>954962</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>467408</t>
+          <t>933385</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1009013</t>
+          <t>974471</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>18783</t>
+          <t>18017</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39022</t>
+          <t>34507</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>284463</t>
+          <t>91860</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>105057</t>
+          <t>75981</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>522168</t>
+          <t>110119</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>303245</t>
+          <t>109877</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>110013</t>
+          <t>90368</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>651618</t>
+          <t>131454</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>424753</t>
+          <t>484503</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>424753</t>
+          <t>484503</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>424753</t>
+          <t>484503</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>694273</t>
+          <t>580336</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>694273</t>
+          <t>580336</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>694273</t>
+          <t>580336</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1119026</t>
+          <t>1064839</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1119026</t>
+          <t>1064839</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1119026</t>
+          <t>1064839</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>677314</t>
+          <t>518138</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>664231</t>
+          <t>503712</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>689012</t>
+          <t>526666</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>434036</t>
+          <t>504218</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>418636</t>
+          <t>485590</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>451928</t>
+          <t>526322</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1111350</t>
+          <t>1022355</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1066395</t>
+          <t>999345</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1188313</t>
+          <t>1043096</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>86,12%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27395</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>150063</t>
+          <t>172023</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>132171</t>
+          <t>149919</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>165463</t>
+          <t>190651</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>164375</t>
+          <t>188814</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>87412</t>
+          <t>168073</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>209330</t>
+          <t>211824</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>691626</t>
+          <t>534928</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>691626</t>
+          <t>534928</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>691626</t>
+          <t>534928</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>584099</t>
+          <t>676241</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>584099</t>
+          <t>676241</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>584099</t>
+          <t>676241</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1275725</t>
+          <t>1211169</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1275725</t>
+          <t>1211169</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1275725</t>
+          <t>1211169</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,17 +3469,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2241856</t>
+          <t>2217872</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2200055</t>
+          <t>2183529</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2279383</t>
+          <t>2244972</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2043434</t>
+          <t>2186466</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1615442</t>
+          <t>2146726</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2223083</t>
+          <t>2227347</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4285290</t>
+          <t>4404338</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3712386</t>
+          <t>4351225</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4486477</t>
+          <t>4453396</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -3582,17 +3582,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>128033</t>
+          <t>126520</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>90506</t>
+          <t>99420</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>169834</t>
+          <t>160863</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>828314</t>
+          <t>665039</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>648665</t>
+          <t>624158</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1256306</t>
+          <t>704779</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>956347</t>
+          <t>791559</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>755160</t>
+          <t>742501</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1529251</t>
+          <t>844672</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2369889</t>
+          <t>2344392</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2369889</t>
+          <t>2344392</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2369889</t>
+          <t>2344392</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2871748</t>
+          <t>2851505</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2871748</t>
+          <t>2851505</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2871748</t>
+          <t>2851505</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>5241637</t>
+          <t>5195897</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5241637</t>
+          <t>5195897</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5241637</t>
+          <t>5195897</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
